--- a/PensamientoAD2026.xlsx
+++ b/PensamientoAD2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/PensamientoC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="8_{96BA18D7-BFC7-46B3-8D27-BF67D73F5CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10E09F0F-8342-4F40-BF98-C858506ABA3A}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="8_{96BA18D7-BFC7-46B3-8D27-BF67D73F5CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C65C144F-9F37-4703-9F6D-410165CA56E1}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D553E2C3-557C-4230-911A-7225414D5E2C}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="127">
   <si>
     <t>16201</t>
   </si>
@@ -411,6 +411,18 @@
   </si>
   <si>
     <t>ernesto.florescordero@tec.mx</t>
+  </si>
+  <si>
+    <t>Ricardo Navarro Gómez</t>
+  </si>
+  <si>
+    <t>ricardo.nav@tec.mx</t>
+  </si>
+  <si>
+    <t>Luis Germán Castañón Cortés</t>
+  </si>
+  <si>
+    <t>luis.cast@tec.mx</t>
   </si>
 </sst>
 </file>
@@ -766,7 +778,7 @@
       <xdr:col>20</xdr:col>
       <xdr:colOff>121173</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>15875</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1119,13 +1131,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B540C7C-6525-4FD8-870B-570711058F68}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:V28"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.7265625" style="1"/>
     <col min="3" max="3" width="32.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="8.7265625" style="1"/>
+    <col min="4" max="4" width="26.36328125" style="1" customWidth="1"/>
+    <col min="5" max="8" width="8.7265625" style="1"/>
     <col min="9" max="9" width="10.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.81640625" style="1" customWidth="1"/>
     <col min="11" max="20" width="8.7265625" style="1"/>
@@ -1254,9 +1266,6 @@
       <c r="U2" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="V2" s="1">
-        <v>1</v>
-      </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
@@ -1314,9 +1323,6 @@
       <c r="U3" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="V3" s="1">
-        <v>2</v>
-      </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
@@ -1431,9 +1437,6 @@
       <c r="U5" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="V5" s="1">
-        <v>3</v>
-      </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
@@ -1550,9 +1553,6 @@
       <c r="U7" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="V7" s="1">
-        <v>4</v>
-      </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
@@ -1610,9 +1610,6 @@
       <c r="U8" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="V8" s="1">
-        <v>5</v>
-      </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" s="29" t="s">
@@ -1670,9 +1667,6 @@
       <c r="U9" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="V9" s="1">
-        <v>6</v>
-      </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
@@ -1789,9 +1783,6 @@
       <c r="U11" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="V11" s="1">
-        <v>7</v>
-      </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="35" t="s">
@@ -1849,9 +1840,6 @@
       <c r="U12" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="V12" s="1">
-        <v>8</v>
-      </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="38" t="s">
@@ -1969,7 +1957,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>53</v>
       </c>
@@ -2027,7 +2015,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="16" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>51</v>
       </c>
@@ -2082,7 +2070,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="17" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>49</v>
       </c>
@@ -2137,7 +2125,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>45</v>
       </c>
@@ -2192,7 +2180,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
         <v>42</v>
       </c>
@@ -2247,7 +2235,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="20" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="23" t="s">
         <v>38</v>
       </c>
@@ -2304,7 +2292,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
         <v>34</v>
       </c>
@@ -2359,7 +2347,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
         <v>32</v>
       </c>
@@ -2414,7 +2402,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="23" t="s">
         <v>28</v>
       </c>
@@ -2469,7 +2457,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="24" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="32" t="s">
         <v>26</v>
       </c>
@@ -2526,7 +2514,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="25" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="35" t="s">
         <v>21</v>
       </c>
@@ -2581,7 +2569,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="38" t="s">
         <v>16</v>
       </c>
@@ -2638,7 +2626,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="27" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="42" t="s">
         <v>10</v>
       </c>
@@ -2716,22 +2704,37 @@
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
     </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C31" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C32" s="47" t="s">
+        <v>123</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C33" s="47" t="s">
+        <v>125</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB27" xr:uid="{5B540C7C-6525-4FD8-870B-570711058F68}">
-    <filterColumn colId="20">
-      <filters>
-        <filter val="Araceli Soto Hernández"/>
-        <filter val="Elizabeth Esquivel González"/>
-        <filter val="Fernando Camacho Ochoa"/>
-        <filter val="Leopoldo Rodríguez Salazar"/>
-        <filter val="Lizethe Pérez Fuertes"/>
-        <filter val="Manuel Iván Casillas del Llano"/>
-        <filter val="María del Consuelo Serrato Arias"/>
-        <filter val="Rene Alejandro Barón Isunza"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AB27" xr:uid="{5B540C7C-6525-4FD8-870B-570711058F68}"/>
+  <hyperlinks>
+    <hyperlink ref="D32" r:id="rId1" xr:uid="{F826BCE4-EB78-4D4A-AB11-3A3C0836AC5A}"/>
+    <hyperlink ref="D33" r:id="rId2" xr:uid="{A7D4C495-3FD5-46A2-89F3-D3BE4C51B873}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/PensamientoAD2026.xlsx
+++ b/PensamientoAD2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/PensamientoC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="8_{96BA18D7-BFC7-46B3-8D27-BF67D73F5CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C65C144F-9F37-4703-9F6D-410165CA56E1}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="8_{96BA18D7-BFC7-46B3-8D27-BF67D73F5CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D1F5C65-4F1F-48FE-AF6D-47EA01FE4B9F}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D553E2C3-557C-4230-911A-7225414D5E2C}"/>
   </bookViews>
@@ -776,7 +776,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>121173</xdr:colOff>
+      <xdr:colOff>124348</xdr:colOff>
       <xdr:row>57</xdr:row>
       <xdr:rowOff>15875</xdr:rowOff>
     </xdr:to>

--- a/PensamientoAD2026.xlsx
+++ b/PensamientoAD2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/PensamientoC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="8_{96BA18D7-BFC7-46B3-8D27-BF67D73F5CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D1F5C65-4F1F-48FE-AF6D-47EA01FE4B9F}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="8_{96BA18D7-BFC7-46B3-8D27-BF67D73F5CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA2810A6-D4FB-4BCD-ABC1-1E4983686BF3}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D553E2C3-557C-4230-911A-7225414D5E2C}"/>
+    <workbookView minimized="1" xWindow="38955" yWindow="5100" windowWidth="14400" windowHeight="7275" xr2:uid="{D553E2C3-557C-4230-911A-7225414D5E2C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1 " sheetId="2" r:id="rId1"/>
@@ -776,7 +776,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>124348</xdr:colOff>
+      <xdr:colOff>670162</xdr:colOff>
       <xdr:row>57</xdr:row>
       <xdr:rowOff>15875</xdr:rowOff>
     </xdr:to>
@@ -1132,15 +1132,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B540C7C-6525-4FD8-870B-570711058F68}">
   <dimension ref="A1:V33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="12.5" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.7265625" style="1"/>
     <col min="3" max="3" width="32.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.36328125" style="1" customWidth="1"/>
-    <col min="5" max="8" width="8.7265625" style="1"/>
+    <col min="4" max="4" width="7.36328125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="0" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="8.7265625" style="1" collapsed="1"/>
+    <col min="7" max="8" width="8.7265625" style="1"/>
     <col min="9" max="9" width="10.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.81640625" style="1" customWidth="1"/>
-    <col min="11" max="20" width="8.7265625" style="1"/>
+    <col min="10" max="10" width="10.81640625" style="1" customWidth="1"/>
+    <col min="11" max="17" width="8.7265625" style="1"/>
+    <col min="18" max="18" width="0" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="8.7265625" style="1" collapsed="1"/>
+    <col min="20" max="20" width="8.7265625" style="1"/>
     <col min="21" max="21" width="25.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="16384" width="8.7265625" style="1"/>
   </cols>

--- a/PensamientoAD2026.xlsx
+++ b/PensamientoAD2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/PensamientoC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="8_{96BA18D7-BFC7-46B3-8D27-BF67D73F5CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA2810A6-D4FB-4BCD-ABC1-1E4983686BF3}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="8_{96BA18D7-BFC7-46B3-8D27-BF67D73F5CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41952096-C43B-47A8-9E60-E59FD4542D8C}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="38955" yWindow="5100" windowWidth="14400" windowHeight="7275" xr2:uid="{D553E2C3-557C-4230-911A-7225414D5E2C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D553E2C3-557C-4230-911A-7225414D5E2C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1 " sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="134">
   <si>
     <t>16201</t>
   </si>
@@ -423,13 +423,34 @@
   </si>
   <si>
     <t>luis.cast@tec.mx</t>
+  </si>
+  <si>
+    <t>baron.rene@tec.mx</t>
+  </si>
+  <si>
+    <t>asotohern@tec.mx</t>
+  </si>
+  <si>
+    <t>manuel_casillas@tec.mx</t>
+  </si>
+  <si>
+    <t>mcserrat@tec.mx</t>
+  </si>
+  <si>
+    <t>liz_esquivel@tec.mx</t>
+  </si>
+  <si>
+    <t>rodriguez.l@tec.mx</t>
+  </si>
+  <si>
+    <t>fcamchooc@tec.mx</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -462,6 +483,18 @@
       <b/>
       <sz val="9"/>
       <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -592,7 +625,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -736,6 +769,8 @@
     <xf numFmtId="49" fontId="5" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -776,7 +811,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>670162</xdr:colOff>
+      <xdr:colOff>676512</xdr:colOff>
       <xdr:row>57</xdr:row>
       <xdr:rowOff>15875</xdr:rowOff>
     </xdr:to>
@@ -1131,12 +1166,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B540C7C-6525-4FD8-870B-570711058F68}">
-  <dimension ref="A1:V33"/>
+  <dimension ref="A1:V42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="12.5" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.7265625" style="1"/>
     <col min="3" max="3" width="32.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.36328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.36328125" style="1" customWidth="1"/>
     <col min="5" max="5" width="0" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="6" max="6" width="8.7265625" style="1" collapsed="1"/>
     <col min="7" max="8" width="8.7265625" style="1"/>
@@ -2733,6 +2768,62 @@
         <v>126</v>
       </c>
     </row>
+    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C36" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="49" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C37" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="49" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C38" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D38" s="49" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C39" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="D39" s="49" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C40" s="30" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40" s="50" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="41" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C41" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="D41" s="49" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="42" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C42" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="D42" s="49" t="s">
+        <v>133</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AB27" xr:uid="{5B540C7C-6525-4FD8-870B-570711058F68}"/>
   <hyperlinks>
